--- a/Electronics/PCBs/Motor Driver/BOM.xlsx
+++ b/Electronics/PCBs/Motor Driver/BOM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
   <si>
     <t>No.</t>
   </si>
@@ -91,109 +91,94 @@
     <t>3</t>
   </si>
   <si>
-    <t>B2B-PH-K-S(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CN-EARS</t>
-  </si>
-  <si>
-    <t>CONN-TH_B2B-PH-K-S</t>
-  </si>
-  <si>
-    <t>C131337</t>
+    <t>B5B-PH-K-S(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CN-SIGNAL</t>
+  </si>
+  <si>
+    <t>CONN-TH_B5B-PH-K-S-LF-SN</t>
+  </si>
+  <si>
+    <t>C157993</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>B5B-PH-K-S(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CN-SIGNAL</t>
-  </si>
-  <si>
-    <t>CONN-TH_B5B-PH-K-S-LF-SN</t>
-  </si>
-  <si>
-    <t>C157993</t>
+    <t>PCA9306DCUR</t>
+  </si>
+  <si>
+    <t>PCA9306</t>
+  </si>
+  <si>
+    <t>SSOP-8_L2.0-W2.3-P0.50-LS3.1-BR</t>
+  </si>
+  <si>
+    <t>TI(德州仪器)</t>
+  </si>
+  <si>
+    <t>C33196</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>PCA9306DCUR</t>
-  </si>
-  <si>
-    <t>PCA9306</t>
-  </si>
-  <si>
-    <t>SSOP-8_L2.0-W2.3-P0.50-LS3.1-BR</t>
-  </si>
-  <si>
-    <t>TI(德州仪器)</t>
-  </si>
-  <si>
-    <t>C33196</t>
+    <t>PCA9685PW,118</t>
+  </si>
+  <si>
+    <t>PCA9685</t>
+  </si>
+  <si>
+    <t>TSSOP-28_L9.7-W4.4-P0.65-LS6.4-TL</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>NXP(恩智浦)</t>
+  </si>
+  <si>
+    <t>C2678753</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>PCA9685PW,118</t>
-  </si>
-  <si>
-    <t>PCA9685</t>
-  </si>
-  <si>
-    <t>TSSOP-28_L9.7-W4.4-P0.65-LS6.4-TL</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>NXP(恩智浦)</t>
-  </si>
-  <si>
-    <t>C2678753</t>
+    <t>220Ω</t>
+  </si>
+  <si>
+    <t>R1,R2,R3,R4,R5,R6,R7,R8,R9,R10,R11,R12,R13,R14</t>
+  </si>
+  <si>
+    <t>R0805</t>
+  </si>
+  <si>
+    <t>0805W8F2200T5E</t>
+  </si>
+  <si>
+    <t>UNI-ROYAL(厚声)</t>
+  </si>
+  <si>
+    <t>C17557</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>220Ω</t>
-  </si>
-  <si>
-    <t>R1,R2,R3,R4,R5,R6,R7,R8,R9,R10,R11,R12,R13,R14</t>
-  </si>
-  <si>
-    <t>R0805</t>
-  </si>
-  <si>
-    <t>0805W8F2200T5E</t>
-  </si>
-  <si>
-    <t>UNI-ROYAL(厚声)</t>
-  </si>
-  <si>
-    <t>C17557</t>
+    <t>200kΩ</t>
+  </si>
+  <si>
+    <t>R-LS</t>
+  </si>
+  <si>
+    <t>0805W8F2003T5E</t>
+  </si>
+  <si>
+    <t>C17539</t>
   </si>
   <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>200kΩ</t>
-  </si>
-  <si>
-    <t>R-LS</t>
-  </si>
-  <si>
-    <t>0805W8F2003T5E</t>
-  </si>
-  <si>
-    <t>C17539</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
   <si>
     <t>2.2kΩ</t>
@@ -582,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="20" customWidth="1"/>
@@ -739,10 +724,10 @@
         <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -750,31 +735,31 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
         <v>37</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
@@ -782,31 +767,31 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" t="s">
-        <v>45</v>
-      </c>
       <c r="G7" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -814,28 +799,28 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" t="s">
         <v>48</v>
-      </c>
-      <c r="B8">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" t="s">
-        <v>52</v>
-      </c>
-      <c r="H8" t="s">
-        <v>53</v>
       </c>
       <c r="I8" t="s">
         <v>54</v>
@@ -849,7 +834,7 @@
         <v>55</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
         <v>56</v>
@@ -858,7 +843,7 @@
         <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
@@ -867,7 +852,7 @@
         <v>58</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I9" t="s">
         <v>59</v>
@@ -876,40 +861,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
         <v>22</v>
       </c>
     </row>
